--- a/planner/archivum/kerelek_2026_09.xlsx
+++ b/planner/archivum/kerelek_2026_09.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -471,69 +471,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Daku Zsuzsa</t>
+          <t>Balogh László</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Enyedi Marcián</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>14-20</t>
-        </is>
-      </c>
+          <t>Berek Sarolta</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10-13</t>
+          <t>3,10,17,23-24,28</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8,20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>5</v>
-      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gulya Réka</t>
+          <t>Berkes Tíbor</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>16-18,21-25,28-29</t>
-        </is>
+          <t>11,25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>2</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -541,16 +532,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hajnal Csilla</t>
+          <t>Daku Zsuzsa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4,11,19</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4-6</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -558,27 +549,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kajner Krisztina</t>
+          <t>Enyedi Marcián</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1-6</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>11,14,18-19,25-26,28,30</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>7,21,23</t>
-        </is>
-      </c>
+          <t>14-20</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10-13</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -586,40 +573,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Karczub János</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>11-13,19</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>Gulya Réka</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Igen</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Katona József</t>
+          <t>Hajnal Csilla</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2,9,16,23,30</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -627,171 +603,183 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kelemen József</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>Kajner Krisztina</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1-6</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>11,14,18-19,25-26,28,30</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,21,23</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Korompai Máté</t>
+          <t>Karczub János</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4,11,14,18</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2,8,10,15,20,22,24,29</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1,3,7,9,16-17,21,23,28,30</t>
-        </is>
-      </c>
+          <t>11-13,19</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Igen</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lambertus Iván</t>
+          <t>Katona József</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4-6,10,18-19,24,27</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>17,20,23,29</t>
-        </is>
-      </c>
+          <t>20-21</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Még 2 hétvégi ügyeletet szeretnék</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pintér Enikő</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5,9,16,23</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>7-8,14-15,21-22</t>
-        </is>
-      </c>
+          <t>Kelemen József</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11-12,19,27</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rákóczi Réka</t>
+          <t>Korompai Máté</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4-6,11-13,19-20,25-27</t>
-        </is>
-      </c>
+          <t>4,11,14,18</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>2,8,10,15,20,22,24,29</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1,3,7,9,16-17,21,23,28,30</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sorbán József</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1-3,7-10,14</t>
-        </is>
-      </c>
+          <t>Kovácsevics József</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>21-30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>19-20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sztermen Márton</t>
+          <t>Lambertus Iván</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4-6,10,18-19,24,27</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3-6,10-13,17-20,24-27</t>
+          <t>17,20,23,29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Szász Kornélia</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>7-18</t>
-        </is>
-      </c>
+          <t>Pintér Enikő</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>7-8,14-15,21-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -800,22 +788,128 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zöldréti Anikó</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>Rákóczi Réka</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4-5,12,18-19,26-27</t>
+          <t>4-6,11-15,17,19-20,25-27</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="n">
-        <v>4</v>
-      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Róbert Beáta</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21-27</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4-6,11,18-20</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sorbán József</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1-3,7-10,14</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sztermen Márton</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3-6,10-13,17-20,24-27</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Szász Kornélia</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7-18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4,25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Zöldréti Anikó</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4-5,12,18-19,26-27</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
